--- a/题库/PY程序设计模拟题1.xlsx
+++ b/题库/PY程序设计模拟题1.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="117">
   <si>
     <t>题号</t>
   </si>
@@ -222,6 +222,9 @@
   </si>
   <si>
     <t>5.0//2.0结果为()。</t>
+  </si>
+  <si>
+    <t>2.0</t>
   </si>
   <si>
     <t>round(2.5) 结果为()。</t>
@@ -536,12 +539,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="5">
+  <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="0.0_ "/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -1192,7 +1194,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1213,9 +1215,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1566,7 +1565,7 @@
       <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="J1" s="7" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1582,7 +1581,7 @@
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
-      <c r="J2" s="8"/>
+      <c r="J2" s="7"/>
     </row>
     <row r="3" ht="34" spans="1:10">
       <c r="A3" s="4">
@@ -1612,7 +1611,7 @@
       <c r="I3" s="3">
         <v>2</v>
       </c>
-      <c r="J3" s="8"/>
+      <c r="J3" s="7"/>
     </row>
     <row r="4" ht="31.5" spans="1:10">
       <c r="A4" s="4">
@@ -1642,7 +1641,7 @@
       <c r="I4" s="3">
         <v>2</v>
       </c>
-      <c r="J4" s="8"/>
+      <c r="J4" s="7"/>
     </row>
     <row r="5" ht="31.5" spans="1:10">
       <c r="A5" s="4">
@@ -1672,7 +1671,7 @@
       <c r="I5" s="3">
         <v>2</v>
       </c>
-      <c r="J5" s="8"/>
+      <c r="J5" s="7"/>
     </row>
     <row r="6" ht="34" spans="1:10">
       <c r="A6" s="4">
@@ -1702,7 +1701,7 @@
       <c r="I6" s="3">
         <v>2</v>
       </c>
-      <c r="J6" s="8"/>
+      <c r="J6" s="7"/>
     </row>
     <row r="7" ht="34" spans="1:10">
       <c r="A7" s="4">
@@ -1732,7 +1731,7 @@
       <c r="I7" s="3">
         <v>2</v>
       </c>
-      <c r="J7" s="8"/>
+      <c r="J7" s="7"/>
     </row>
     <row r="8" ht="17" spans="1:10">
       <c r="A8" s="4">
@@ -1762,7 +1761,7 @@
       <c r="I8" s="3">
         <v>2</v>
       </c>
-      <c r="J8" s="8"/>
+      <c r="J8" s="7"/>
     </row>
     <row r="9" ht="17" spans="1:10">
       <c r="A9" s="4">
@@ -1792,7 +1791,7 @@
       <c r="I9" s="3">
         <v>2</v>
       </c>
-      <c r="J9" s="8"/>
+      <c r="J9" s="7"/>
     </row>
     <row r="10" ht="17" spans="1:10">
       <c r="A10" s="4">
@@ -1813,8 +1812,8 @@
       <c r="F10" s="3">
         <v>3</v>
       </c>
-      <c r="G10" s="7">
-        <v>2</v>
+      <c r="G10" s="5" t="s">
+        <v>41</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>22</v>
@@ -1822,7 +1821,7 @@
       <c r="I10" s="3">
         <v>2</v>
       </c>
-      <c r="J10" s="8"/>
+      <c r="J10" s="7"/>
     </row>
     <row r="11" ht="17" spans="1:10">
       <c r="A11" s="4">
@@ -1832,7 +1831,7 @@
         <v>10</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D11" s="3">
         <v>2</v>
@@ -1843,8 +1842,8 @@
       <c r="F11" s="3">
         <v>3</v>
       </c>
-      <c r="G11" s="7">
-        <v>2</v>
+      <c r="G11" s="5" t="s">
+        <v>41</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>35</v>
@@ -1852,7 +1851,7 @@
       <c r="I11" s="3">
         <v>2</v>
       </c>
-      <c r="J11" s="8"/>
+      <c r="J11" s="7"/>
     </row>
     <row r="12" ht="51" spans="1:10">
       <c r="A12" s="4">
@@ -1862,19 +1861,19 @@
         <v>10</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>22</v>
@@ -1882,7 +1881,7 @@
       <c r="I12" s="3">
         <v>2</v>
       </c>
-      <c r="J12" s="8"/>
+      <c r="J12" s="7"/>
     </row>
     <row r="13" ht="34" spans="1:10">
       <c r="A13" s="4">
@@ -1892,7 +1891,7 @@
         <v>10</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D13" s="3">
         <v>5</v>
@@ -1912,7 +1911,7 @@
       <c r="I13" s="3">
         <v>2</v>
       </c>
-      <c r="J13" s="8"/>
+      <c r="J13" s="7"/>
     </row>
     <row r="14" ht="34" spans="1:10">
       <c r="A14" s="4">
@@ -1922,19 +1921,19 @@
         <v>10</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>22</v>
@@ -1942,7 +1941,7 @@
       <c r="I14" s="3">
         <v>2</v>
       </c>
-      <c r="J14" s="8"/>
+      <c r="J14" s="7"/>
     </row>
     <row r="15" ht="104" spans="1:10">
       <c r="A15" s="4">
@@ -1952,19 +1951,19 @@
         <v>10</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>22</v>
@@ -1972,7 +1971,7 @@
       <c r="I15" s="3">
         <v>2</v>
       </c>
-      <c r="J15" s="8"/>
+      <c r="J15" s="7"/>
     </row>
     <row r="16" ht="34" spans="1:10">
       <c r="A16" s="4">
@@ -1982,19 +1981,19 @@
         <v>10</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>28</v>
@@ -2002,7 +2001,7 @@
       <c r="I16" s="3">
         <v>2</v>
       </c>
-      <c r="J16" s="8"/>
+      <c r="J16" s="7"/>
     </row>
     <row r="17" ht="51" spans="1:10">
       <c r="A17" s="4">
@@ -2012,19 +2011,19 @@
         <v>10</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>16</v>
@@ -2032,11 +2031,11 @@
       <c r="I17" s="3">
         <v>2</v>
       </c>
-      <c r="J17" s="8"/>
+      <c r="J17" s="7"/>
     </row>
     <row r="18" ht="17" spans="1:10">
       <c r="A18" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
@@ -2046,83 +2045,83 @@
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
-      <c r="J18" s="8"/>
+      <c r="J18" s="7"/>
     </row>
     <row r="19" ht="34" spans="1:10">
       <c r="A19" s="4">
         <v>16</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
       <c r="H19" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I19" s="3">
         <v>2</v>
       </c>
-      <c r="J19" s="8"/>
+      <c r="J19" s="7"/>
     </row>
     <row r="20" ht="31.5" spans="1:10">
       <c r="A20" s="4">
         <v>17</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
       <c r="H20" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I20" s="3">
         <v>2</v>
       </c>
-      <c r="J20" s="8"/>
+      <c r="J20" s="7"/>
     </row>
     <row r="21" ht="34" spans="1:10">
       <c r="A21" s="4">
         <v>18</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
       <c r="H21" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I21" s="3">
         <v>2</v>
       </c>
-      <c r="J21" s="8"/>
+      <c r="J21" s="7"/>
     </row>
     <row r="22" ht="34" spans="1:10">
       <c r="A22" s="4">
         <v>19</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
@@ -2134,61 +2133,61 @@
       <c r="I22" s="3">
         <v>2</v>
       </c>
-      <c r="J22" s="8"/>
+      <c r="J22" s="7"/>
     </row>
     <row r="23" ht="34" spans="1:10">
       <c r="A23" s="4">
         <v>20</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
       <c r="G23" s="3"/>
       <c r="H23" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I23" s="3">
         <v>2</v>
       </c>
-      <c r="J23" s="8"/>
+      <c r="J23" s="7"/>
     </row>
     <row r="24" ht="34" spans="1:10">
       <c r="A24" s="4">
         <v>21</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D24" s="3"/>
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
       <c r="G24" s="3"/>
       <c r="H24" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I24" s="3">
         <v>2</v>
       </c>
-      <c r="J24" s="8"/>
+      <c r="J24" s="7"/>
     </row>
     <row r="25" ht="51" spans="1:10">
       <c r="A25" s="4">
         <v>22</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
@@ -2200,17 +2199,17 @@
       <c r="I25" s="3">
         <v>2</v>
       </c>
-      <c r="J25" s="8"/>
+      <c r="J25" s="7"/>
     </row>
     <row r="26" ht="17" spans="1:10">
       <c r="A26" s="4">
         <v>23</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D26" s="3"/>
       <c r="E26" s="3"/>
@@ -2222,17 +2221,17 @@
       <c r="I26" s="3">
         <v>2</v>
       </c>
-      <c r="J26" s="8"/>
+      <c r="J26" s="7"/>
     </row>
     <row r="27" ht="68" spans="1:10">
       <c r="A27" s="4">
         <v>24</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D27" s="3"/>
       <c r="E27" s="3"/>
@@ -2244,83 +2243,83 @@
       <c r="I27" s="3">
         <v>2</v>
       </c>
-      <c r="J27" s="8"/>
+      <c r="J27" s="7"/>
     </row>
     <row r="28" ht="68" spans="1:10">
       <c r="A28" s="4">
         <v>25</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D28" s="3"/>
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
       <c r="G28" s="3"/>
       <c r="H28" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I28" s="3">
         <v>2</v>
       </c>
-      <c r="J28" s="8"/>
+      <c r="J28" s="7"/>
     </row>
     <row r="29" ht="51" spans="1:10">
       <c r="A29" s="4">
         <v>26</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D29" s="3"/>
       <c r="E29" s="3"/>
       <c r="F29" s="3"/>
       <c r="G29" s="3"/>
       <c r="H29" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I29" s="3">
         <v>2</v>
       </c>
-      <c r="J29" s="8"/>
+      <c r="J29" s="7"/>
     </row>
     <row r="30" ht="48.5" spans="1:10">
       <c r="A30" s="4">
         <v>27</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D30" s="3"/>
       <c r="E30" s="3"/>
       <c r="F30" s="3"/>
       <c r="G30" s="3"/>
       <c r="H30" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I30" s="3">
         <v>2</v>
       </c>
-      <c r="J30" s="8"/>
+      <c r="J30" s="7"/>
     </row>
     <row r="31" ht="34" spans="1:10">
       <c r="A31" s="4">
         <v>28</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D31" s="3"/>
       <c r="E31" s="3"/>
@@ -2332,17 +2331,17 @@
       <c r="I31" s="3">
         <v>2</v>
       </c>
-      <c r="J31" s="8"/>
+      <c r="J31" s="7"/>
     </row>
     <row r="32" ht="34" spans="1:10">
       <c r="A32" s="4">
         <v>29</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D32" s="3"/>
       <c r="E32" s="3"/>
@@ -2354,17 +2353,17 @@
       <c r="I32" s="3">
         <v>2</v>
       </c>
-      <c r="J32" s="8"/>
+      <c r="J32" s="7"/>
     </row>
     <row r="33" ht="34" spans="1:10">
       <c r="A33" s="4">
         <v>30</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D33" s="3"/>
       <c r="E33" s="3"/>
@@ -2376,11 +2375,11 @@
       <c r="I33" s="3">
         <v>2</v>
       </c>
-      <c r="J33" s="8"/>
+      <c r="J33" s="7"/>
     </row>
     <row r="34" ht="17" spans="1:10">
       <c r="A34" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
@@ -2390,23 +2389,23 @@
       <c r="G34" s="3"/>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
-      <c r="J34" s="8"/>
+      <c r="J34" s="7"/>
     </row>
     <row r="35" ht="60.5" spans="1:10">
       <c r="A35" s="4">
         <v>31</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F35" s="3"/>
       <c r="G35" s="3"/>
@@ -2416,23 +2415,23 @@
       <c r="I35" s="3">
         <v>1</v>
       </c>
-      <c r="J35" s="8"/>
+      <c r="J35" s="7"/>
     </row>
     <row r="36" ht="46" spans="1:10">
       <c r="A36" s="4">
         <v>32</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C36" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E36" s="3" t="s">
         <v>96</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>95</v>
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="3"/>
@@ -2442,23 +2441,23 @@
       <c r="I36" s="3">
         <v>1</v>
       </c>
-      <c r="J36" s="8"/>
+      <c r="J36" s="7"/>
     </row>
     <row r="37" ht="17" spans="1:10">
       <c r="A37" s="4">
         <v>33</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F37" s="3"/>
       <c r="G37" s="3"/>
@@ -2468,23 +2467,23 @@
       <c r="I37" s="3">
         <v>1</v>
       </c>
-      <c r="J37" s="8"/>
+      <c r="J37" s="7"/>
     </row>
     <row r="38" ht="48.5" spans="1:10">
       <c r="A38" s="4">
         <v>34</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F38" s="3"/>
       <c r="G38" s="3"/>
@@ -2494,23 +2493,23 @@
       <c r="I38" s="3">
         <v>1</v>
       </c>
-      <c r="J38" s="8"/>
+      <c r="J38" s="7"/>
     </row>
     <row r="39" ht="43.5" spans="1:10">
       <c r="A39" s="4">
         <v>35</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="3"/>
@@ -2520,23 +2519,23 @@
       <c r="I39" s="3">
         <v>1</v>
       </c>
-      <c r="J39" s="8"/>
+      <c r="J39" s="7"/>
     </row>
     <row r="40" ht="31.5" spans="1:10">
       <c r="A40" s="4">
         <v>36</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F40" s="3"/>
       <c r="G40" s="3"/>
@@ -2546,23 +2545,23 @@
       <c r="I40" s="3">
         <v>1</v>
       </c>
-      <c r="J40" s="8"/>
+      <c r="J40" s="7"/>
     </row>
     <row r="41" ht="31.5" spans="1:10">
       <c r="A41" s="4">
         <v>37</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3"/>
@@ -2572,23 +2571,23 @@
       <c r="I41" s="3">
         <v>1</v>
       </c>
-      <c r="J41" s="8"/>
+      <c r="J41" s="7"/>
     </row>
     <row r="42" ht="43.5" spans="1:10">
       <c r="A42" s="4">
         <v>38</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F42" s="3"/>
       <c r="G42" s="3"/>
@@ -2598,23 +2597,23 @@
       <c r="I42" s="3">
         <v>1</v>
       </c>
-      <c r="J42" s="8"/>
+      <c r="J42" s="7"/>
     </row>
     <row r="43" ht="34" spans="1:10">
       <c r="A43" s="4">
         <v>39</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="3"/>
@@ -2624,23 +2623,23 @@
       <c r="I43" s="3">
         <v>1</v>
       </c>
-      <c r="J43" s="8"/>
+      <c r="J43" s="7"/>
     </row>
     <row r="44" ht="48.5" spans="1:10">
       <c r="A44" s="4">
         <v>40</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3"/>
@@ -2650,11 +2649,11 @@
       <c r="I44" s="3">
         <v>1</v>
       </c>
-      <c r="J44" s="8"/>
+      <c r="J44" s="7"/>
     </row>
     <row r="45" ht="17" spans="1:10">
       <c r="A45" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
@@ -2664,30 +2663,30 @@
       <c r="G45" s="3"/>
       <c r="H45" s="3"/>
       <c r="I45" s="3"/>
-      <c r="J45" s="8"/>
+      <c r="J45" s="7"/>
     </row>
     <row r="46" ht="46" spans="1:10">
       <c r="A46" s="4">
         <v>41</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D46" s="3"/>
       <c r="E46" s="3"/>
       <c r="F46" s="3"/>
       <c r="G46" s="3"/>
       <c r="H46" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I46" s="3">
         <v>10</v>
       </c>
-      <c r="J46" s="8" t="s">
-        <v>108</v>
+      <c r="J46" s="7" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="47" ht="68" spans="1:10">
@@ -2695,28 +2694,28 @@
         <v>42</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D47" s="3"/>
       <c r="E47" s="3"/>
       <c r="F47" s="3"/>
       <c r="G47" s="3"/>
       <c r="H47" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I47" s="3">
         <v>10</v>
       </c>
-      <c r="J47" s="8" t="s">
-        <v>111</v>
+      <c r="J47" s="7" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="48" ht="17" spans="1:10">
       <c r="A48" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B48" s="4"/>
       <c r="C48" s="4"/>
@@ -2726,30 +2725,30 @@
       <c r="G48" s="3"/>
       <c r="H48" s="3"/>
       <c r="I48" s="3"/>
-      <c r="J48" s="8"/>
+      <c r="J48" s="7"/>
     </row>
     <row r="49" ht="204" spans="1:10">
       <c r="A49" s="4">
         <v>43</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D49" s="3"/>
       <c r="E49" s="3"/>
       <c r="F49" s="3"/>
       <c r="G49" s="3"/>
       <c r="H49" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I49" s="3">
         <v>10</v>
       </c>
-      <c r="J49" s="8" t="s">
-        <v>115</v>
+      <c r="J49" s="7" t="s">
+        <v>116</v>
       </c>
     </row>
   </sheetData>

--- a/题库/PY程序设计模拟题1.xlsx
+++ b/题库/PY程序设计模拟题1.xlsx
@@ -293,9 +293,42 @@
     <t>([2,3,4])</t>
   </si>
   <si>
-    <t xml:space="preserve">  print("Equal") 
+    <r>
+      <t>执行下列</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Python</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>语句后的显示结果是（）。
+x=3
+y=2.0
+if(x==y):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+  print("Equal") 
 else: 
   print("Not Equal") </t>
+    </r>
   </si>
   <si>
     <t>Equal</t>
@@ -563,6 +596,12 @@
       <sz val="11.5"/>
       <color rgb="FF0F1115"/>
       <name val="Segoe UI"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11.5"/>
+      <color rgb="FF0F1115"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -710,12 +749,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11.5"/>
-      <color rgb="FF0F1115"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <i/>
       <sz val="11.25"/>
       <color rgb="FF0F1115"/>
@@ -1064,137 +1097,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1214,6 +1247,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1565,7 +1601,7 @@
       <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="J1" s="8" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1581,7 +1617,7 @@
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
-      <c r="J2" s="7"/>
+      <c r="J2" s="8"/>
     </row>
     <row r="3" ht="34" spans="1:10">
       <c r="A3" s="4">
@@ -1611,7 +1647,7 @@
       <c r="I3" s="3">
         <v>2</v>
       </c>
-      <c r="J3" s="7"/>
+      <c r="J3" s="8"/>
     </row>
     <row r="4" ht="31.5" spans="1:10">
       <c r="A4" s="4">
@@ -1641,7 +1677,7 @@
       <c r="I4" s="3">
         <v>2</v>
       </c>
-      <c r="J4" s="7"/>
+      <c r="J4" s="8"/>
     </row>
     <row r="5" ht="31.5" spans="1:10">
       <c r="A5" s="4">
@@ -1671,7 +1707,7 @@
       <c r="I5" s="3">
         <v>2</v>
       </c>
-      <c r="J5" s="7"/>
+      <c r="J5" s="8"/>
     </row>
     <row r="6" ht="34" spans="1:10">
       <c r="A6" s="4">
@@ -1701,7 +1737,7 @@
       <c r="I6" s="3">
         <v>2</v>
       </c>
-      <c r="J6" s="7"/>
+      <c r="J6" s="8"/>
     </row>
     <row r="7" ht="34" spans="1:10">
       <c r="A7" s="4">
@@ -1731,7 +1767,7 @@
       <c r="I7" s="3">
         <v>2</v>
       </c>
-      <c r="J7" s="7"/>
+      <c r="J7" s="8"/>
     </row>
     <row r="8" ht="17" spans="1:10">
       <c r="A8" s="4">
@@ -1761,7 +1797,7 @@
       <c r="I8" s="3">
         <v>2</v>
       </c>
-      <c r="J8" s="7"/>
+      <c r="J8" s="8"/>
     </row>
     <row r="9" ht="17" spans="1:10">
       <c r="A9" s="4">
@@ -1791,7 +1827,7 @@
       <c r="I9" s="3">
         <v>2</v>
       </c>
-      <c r="J9" s="7"/>
+      <c r="J9" s="8"/>
     </row>
     <row r="10" ht="17" spans="1:10">
       <c r="A10" s="4">
@@ -1821,7 +1857,7 @@
       <c r="I10" s="3">
         <v>2</v>
       </c>
-      <c r="J10" s="7"/>
+      <c r="J10" s="8"/>
     </row>
     <row r="11" ht="17" spans="1:10">
       <c r="A11" s="4">
@@ -1851,7 +1887,7 @@
       <c r="I11" s="3">
         <v>2</v>
       </c>
-      <c r="J11" s="7"/>
+      <c r="J11" s="8"/>
     </row>
     <row r="12" ht="51" spans="1:10">
       <c r="A12" s="4">
@@ -1881,7 +1917,7 @@
       <c r="I12" s="3">
         <v>2</v>
       </c>
-      <c r="J12" s="7"/>
+      <c r="J12" s="8"/>
     </row>
     <row r="13" ht="34" spans="1:10">
       <c r="A13" s="4">
@@ -1911,7 +1947,7 @@
       <c r="I13" s="3">
         <v>2</v>
       </c>
-      <c r="J13" s="7"/>
+      <c r="J13" s="8"/>
     </row>
     <row r="14" ht="34" spans="1:10">
       <c r="A14" s="4">
@@ -1941,7 +1977,7 @@
       <c r="I14" s="3">
         <v>2</v>
       </c>
-      <c r="J14" s="7"/>
+      <c r="J14" s="8"/>
     </row>
     <row r="15" ht="104" spans="1:10">
       <c r="A15" s="4">
@@ -1971,7 +2007,7 @@
       <c r="I15" s="3">
         <v>2</v>
       </c>
-      <c r="J15" s="7"/>
+      <c r="J15" s="8"/>
     </row>
     <row r="16" ht="34" spans="1:10">
       <c r="A16" s="4">
@@ -2001,16 +2037,16 @@
       <c r="I16" s="3">
         <v>2</v>
       </c>
-      <c r="J16" s="7"/>
-    </row>
-    <row r="17" ht="51" spans="1:10">
+      <c r="J16" s="8"/>
+    </row>
+    <row r="17" ht="128.5" spans="1:10">
       <c r="A17" s="4">
         <v>15</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="7" t="s">
         <v>64</v>
       </c>
       <c r="D17" s="3" t="s">
@@ -2031,7 +2067,7 @@
       <c r="I17" s="3">
         <v>2</v>
       </c>
-      <c r="J17" s="7"/>
+      <c r="J17" s="8"/>
     </row>
     <row r="18" ht="17" spans="1:10">
       <c r="A18" s="4" t="s">
@@ -2045,7 +2081,7 @@
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
-      <c r="J18" s="7"/>
+      <c r="J18" s="8"/>
     </row>
     <row r="19" ht="34" spans="1:10">
       <c r="A19" s="4">
@@ -2067,7 +2103,7 @@
       <c r="I19" s="3">
         <v>2</v>
       </c>
-      <c r="J19" s="7"/>
+      <c r="J19" s="8"/>
     </row>
     <row r="20" ht="31.5" spans="1:10">
       <c r="A20" s="4">
@@ -2089,7 +2125,7 @@
       <c r="I20" s="3">
         <v>2</v>
       </c>
-      <c r="J20" s="7"/>
+      <c r="J20" s="8"/>
     </row>
     <row r="21" ht="34" spans="1:10">
       <c r="A21" s="4">
@@ -2111,7 +2147,7 @@
       <c r="I21" s="3">
         <v>2</v>
       </c>
-      <c r="J21" s="7"/>
+      <c r="J21" s="8"/>
     </row>
     <row r="22" ht="34" spans="1:10">
       <c r="A22" s="4">
@@ -2133,7 +2169,7 @@
       <c r="I22" s="3">
         <v>2</v>
       </c>
-      <c r="J22" s="7"/>
+      <c r="J22" s="8"/>
     </row>
     <row r="23" ht="34" spans="1:10">
       <c r="A23" s="4">
@@ -2155,7 +2191,7 @@
       <c r="I23" s="3">
         <v>2</v>
       </c>
-      <c r="J23" s="7"/>
+      <c r="J23" s="8"/>
     </row>
     <row r="24" ht="34" spans="1:10">
       <c r="A24" s="4">
@@ -2177,7 +2213,7 @@
       <c r="I24" s="3">
         <v>2</v>
       </c>
-      <c r="J24" s="7"/>
+      <c r="J24" s="8"/>
     </row>
     <row r="25" ht="51" spans="1:10">
       <c r="A25" s="4">
@@ -2199,7 +2235,7 @@
       <c r="I25" s="3">
         <v>2</v>
       </c>
-      <c r="J25" s="7"/>
+      <c r="J25" s="8"/>
     </row>
     <row r="26" ht="17" spans="1:10">
       <c r="A26" s="4">
@@ -2221,7 +2257,7 @@
       <c r="I26" s="3">
         <v>2</v>
       </c>
-      <c r="J26" s="7"/>
+      <c r="J26" s="8"/>
     </row>
     <row r="27" ht="68" spans="1:10">
       <c r="A27" s="4">
@@ -2243,7 +2279,7 @@
       <c r="I27" s="3">
         <v>2</v>
       </c>
-      <c r="J27" s="7"/>
+      <c r="J27" s="8"/>
     </row>
     <row r="28" ht="68" spans="1:10">
       <c r="A28" s="4">
@@ -2265,7 +2301,7 @@
       <c r="I28" s="3">
         <v>2</v>
       </c>
-      <c r="J28" s="7"/>
+      <c r="J28" s="8"/>
     </row>
     <row r="29" ht="51" spans="1:10">
       <c r="A29" s="4">
@@ -2287,7 +2323,7 @@
       <c r="I29" s="3">
         <v>2</v>
       </c>
-      <c r="J29" s="7"/>
+      <c r="J29" s="8"/>
     </row>
     <row r="30" ht="48.5" spans="1:10">
       <c r="A30" s="4">
@@ -2309,7 +2345,7 @@
       <c r="I30" s="3">
         <v>2</v>
       </c>
-      <c r="J30" s="7"/>
+      <c r="J30" s="8"/>
     </row>
     <row r="31" ht="34" spans="1:10">
       <c r="A31" s="4">
@@ -2331,7 +2367,7 @@
       <c r="I31" s="3">
         <v>2</v>
       </c>
-      <c r="J31" s="7"/>
+      <c r="J31" s="8"/>
     </row>
     <row r="32" ht="34" spans="1:10">
       <c r="A32" s="4">
@@ -2353,7 +2389,7 @@
       <c r="I32" s="3">
         <v>2</v>
       </c>
-      <c r="J32" s="7"/>
+      <c r="J32" s="8"/>
     </row>
     <row r="33" ht="34" spans="1:10">
       <c r="A33" s="4">
@@ -2375,7 +2411,7 @@
       <c r="I33" s="3">
         <v>2</v>
       </c>
-      <c r="J33" s="7"/>
+      <c r="J33" s="8"/>
     </row>
     <row r="34" ht="17" spans="1:10">
       <c r="A34" s="4" t="s">
@@ -2389,7 +2425,7 @@
       <c r="G34" s="3"/>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
-      <c r="J34" s="7"/>
+      <c r="J34" s="8"/>
     </row>
     <row r="35" ht="60.5" spans="1:10">
       <c r="A35" s="4">
@@ -2415,7 +2451,7 @@
       <c r="I35" s="3">
         <v>1</v>
       </c>
-      <c r="J35" s="7"/>
+      <c r="J35" s="8"/>
     </row>
     <row r="36" ht="46" spans="1:10">
       <c r="A36" s="4">
@@ -2441,7 +2477,7 @@
       <c r="I36" s="3">
         <v>1</v>
       </c>
-      <c r="J36" s="7"/>
+      <c r="J36" s="8"/>
     </row>
     <row r="37" ht="17" spans="1:10">
       <c r="A37" s="4">
@@ -2467,7 +2503,7 @@
       <c r="I37" s="3">
         <v>1</v>
       </c>
-      <c r="J37" s="7"/>
+      <c r="J37" s="8"/>
     </row>
     <row r="38" ht="48.5" spans="1:10">
       <c r="A38" s="4">
@@ -2493,7 +2529,7 @@
       <c r="I38" s="3">
         <v>1</v>
       </c>
-      <c r="J38" s="7"/>
+      <c r="J38" s="8"/>
     </row>
     <row r="39" ht="43.5" spans="1:10">
       <c r="A39" s="4">
@@ -2519,7 +2555,7 @@
       <c r="I39" s="3">
         <v>1</v>
       </c>
-      <c r="J39" s="7"/>
+      <c r="J39" s="8"/>
     </row>
     <row r="40" ht="31.5" spans="1:10">
       <c r="A40" s="4">
@@ -2545,7 +2581,7 @@
       <c r="I40" s="3">
         <v>1</v>
       </c>
-      <c r="J40" s="7"/>
+      <c r="J40" s="8"/>
     </row>
     <row r="41" ht="31.5" spans="1:10">
       <c r="A41" s="4">
@@ -2571,7 +2607,7 @@
       <c r="I41" s="3">
         <v>1</v>
       </c>
-      <c r="J41" s="7"/>
+      <c r="J41" s="8"/>
     </row>
     <row r="42" ht="43.5" spans="1:10">
       <c r="A42" s="4">
@@ -2597,7 +2633,7 @@
       <c r="I42" s="3">
         <v>1</v>
       </c>
-      <c r="J42" s="7"/>
+      <c r="J42" s="8"/>
     </row>
     <row r="43" ht="34" spans="1:10">
       <c r="A43" s="4">
@@ -2623,7 +2659,7 @@
       <c r="I43" s="3">
         <v>1</v>
       </c>
-      <c r="J43" s="7"/>
+      <c r="J43" s="8"/>
     </row>
     <row r="44" ht="48.5" spans="1:10">
       <c r="A44" s="4">
@@ -2649,7 +2685,7 @@
       <c r="I44" s="3">
         <v>1</v>
       </c>
-      <c r="J44" s="7"/>
+      <c r="J44" s="8"/>
     </row>
     <row r="45" ht="17" spans="1:10">
       <c r="A45" s="4" t="s">
@@ -2663,7 +2699,7 @@
       <c r="G45" s="3"/>
       <c r="H45" s="3"/>
       <c r="I45" s="3"/>
-      <c r="J45" s="7"/>
+      <c r="J45" s="8"/>
     </row>
     <row r="46" ht="46" spans="1:10">
       <c r="A46" s="4">
@@ -2685,7 +2721,7 @@
       <c r="I46" s="3">
         <v>10</v>
       </c>
-      <c r="J46" s="7" t="s">
+      <c r="J46" s="8" t="s">
         <v>109</v>
       </c>
     </row>
@@ -2709,7 +2745,7 @@
       <c r="I47" s="3">
         <v>10</v>
       </c>
-      <c r="J47" s="7" t="s">
+      <c r="J47" s="8" t="s">
         <v>112</v>
       </c>
     </row>
@@ -2725,7 +2761,7 @@
       <c r="G48" s="3"/>
       <c r="H48" s="3"/>
       <c r="I48" s="3"/>
-      <c r="J48" s="7"/>
+      <c r="J48" s="8"/>
     </row>
     <row r="49" ht="204" spans="1:10">
       <c r="A49" s="4">
@@ -2747,7 +2783,7 @@
       <c r="I49" s="3">
         <v>10</v>
       </c>
-      <c r="J49" s="7" t="s">
+      <c r="J49" s="8" t="s">
         <v>116</v>
       </c>
     </row>
